--- a/arte_comercial/downloads/master.xlsx
+++ b/arte_comercial/downloads/master.xlsx
@@ -1,15 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3c062993eaa45f7e/.vscode/JARVIS/arte_comercial/downloads/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_5A6D22ED9193CA21D52D4CCC3D29265B787A4780" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1357,8 +1376,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1421,13 +1440,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1465,7 +1492,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1499,6 +1526,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1533,9 +1561,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1708,11 +1737,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J199"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1744,7 +1773,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1776,7 +1805,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1808,7 +1837,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1840,7 +1869,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1857,7 +1886,7 @@
         <v>5071.43</v>
       </c>
       <c r="F5">
-        <v>40571.44</v>
+        <v>40571.440000000002</v>
       </c>
       <c r="G5" t="s">
         <v>423</v>
@@ -1872,7 +1901,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1904,7 +1933,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1936,7 +1965,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1950,7 +1979,7 @@
         <v>28</v>
       </c>
       <c r="E8">
-        <v>144.27</v>
+        <v>144.27000000000001</v>
       </c>
       <c r="F8">
         <v>4039.56</v>
@@ -1968,7 +1997,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1985,7 +2014,7 @@
         <v>51.37</v>
       </c>
       <c r="F9">
-        <v>513.7</v>
+        <v>513.70000000000005</v>
       </c>
       <c r="G9" t="s">
         <v>423</v>
@@ -2000,7 +2029,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -2032,7 +2061,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2064,7 +2093,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -2096,7 +2125,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -2128,7 +2157,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -2160,7 +2189,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -2192,7 +2221,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -2224,7 +2253,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -2256,7 +2285,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -2288,7 +2317,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -2320,7 +2349,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -2352,7 +2381,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -2384,7 +2413,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -2416,7 +2445,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -2448,7 +2477,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -2480,7 +2509,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -2512,7 +2541,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -2544,7 +2573,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -2576,7 +2605,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -2590,7 +2619,7 @@
         <v>7</v>
       </c>
       <c r="E28">
-        <v>549.9400000000001</v>
+        <v>549.94000000000005</v>
       </c>
       <c r="F28">
         <v>3849.58</v>
@@ -2608,7 +2637,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -2640,7 +2669,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -2672,7 +2701,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -2704,7 +2733,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -2718,7 +2747,7 @@
         <v>2</v>
       </c>
       <c r="E32">
-        <v>954.4400000000001</v>
+        <v>954.44</v>
       </c>
       <c r="F32">
         <v>1908.88</v>
@@ -2736,7 +2765,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -2768,7 +2797,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -2800,7 +2829,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -2832,7 +2861,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -2846,10 +2875,10 @@
         <v>2</v>
       </c>
       <c r="E36">
-        <v>22681.2</v>
+        <v>22681.200000000001</v>
       </c>
       <c r="F36">
-        <v>45362.4</v>
+        <v>45362.400000000001</v>
       </c>
       <c r="G36" t="s">
         <v>423</v>
@@ -2864,7 +2893,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>13</v>
       </c>
@@ -2896,7 +2925,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>14</v>
       </c>
@@ -2910,10 +2939,10 @@
         <v>4</v>
       </c>
       <c r="E38">
-        <v>24189.04</v>
+        <v>24189.040000000001</v>
       </c>
       <c r="F38">
-        <v>96756.16</v>
+        <v>96756.160000000003</v>
       </c>
       <c r="G38" t="s">
         <v>423</v>
@@ -2928,7 +2957,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -2942,10 +2971,10 @@
         <v>1</v>
       </c>
       <c r="E39">
-        <v>43316.8</v>
+        <v>43316.800000000003</v>
       </c>
       <c r="F39">
-        <v>43316.8</v>
+        <v>43316.800000000003</v>
       </c>
       <c r="G39" t="s">
         <v>423</v>
@@ -2960,7 +2989,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>16</v>
       </c>
@@ -2992,7 +3021,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>17</v>
       </c>
@@ -3024,7 +3053,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -3056,7 +3085,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>19</v>
       </c>
@@ -3088,7 +3117,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>20</v>
       </c>
@@ -3120,7 +3149,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>21</v>
       </c>
@@ -3152,7 +3181,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -3184,7 +3213,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>23</v>
       </c>
@@ -3216,7 +3245,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>24</v>
       </c>
@@ -3248,7 +3277,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>25</v>
       </c>
@@ -3280,7 +3309,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>26</v>
       </c>
@@ -3312,7 +3341,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>27</v>
       </c>
@@ -3344,7 +3373,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>28</v>
       </c>
@@ -3376,7 +3405,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>29</v>
       </c>
@@ -3408,7 +3437,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>30</v>
       </c>
@@ -3440,7 +3469,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>31</v>
       </c>
@@ -3472,7 +3501,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>32</v>
       </c>
@@ -3504,7 +3533,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>33</v>
       </c>
@@ -3536,7 +3565,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>34</v>
       </c>
@@ -3568,7 +3597,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>35</v>
       </c>
@@ -3600,7 +3629,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>36</v>
       </c>
@@ -3617,7 +3646,7 @@
         <v>197.91</v>
       </c>
       <c r="F60">
-        <v>2177.01</v>
+        <v>2177.0100000000002</v>
       </c>
       <c r="G60" t="s">
         <v>423</v>
@@ -3632,7 +3661,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>37</v>
       </c>
@@ -3664,7 +3693,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>38</v>
       </c>
@@ -3696,7 +3725,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>39</v>
       </c>
@@ -3710,7 +3739,7 @@
         <v>49</v>
       </c>
       <c r="E63">
-        <v>39.3</v>
+        <v>39.299999999999997</v>
       </c>
       <c r="F63">
         <v>1925.7</v>
@@ -3728,7 +3757,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>40</v>
       </c>
@@ -3760,7 +3789,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>41</v>
       </c>
@@ -3777,7 +3806,7 @@
         <v>39.99</v>
       </c>
       <c r="F65">
-        <v>8797.799999999999</v>
+        <v>8797.7999999999993</v>
       </c>
       <c r="G65" t="s">
         <v>423</v>
@@ -3792,7 +3821,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>42</v>
       </c>
@@ -3824,7 +3853,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>43</v>
       </c>
@@ -3856,7 +3885,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>44</v>
       </c>
@@ -3888,7 +3917,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>45</v>
       </c>
@@ -3920,7 +3949,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>46</v>
       </c>
@@ -3952,7 +3981,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>47</v>
       </c>
@@ -3984,7 +4013,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>48</v>
       </c>
@@ -4001,7 +4030,7 @@
         <v>223.91</v>
       </c>
       <c r="F72">
-        <v>2463.01</v>
+        <v>2463.0100000000002</v>
       </c>
       <c r="G72" t="s">
         <v>423</v>
@@ -4016,7 +4045,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>49</v>
       </c>
@@ -4048,7 +4077,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>50</v>
       </c>
@@ -4062,7 +4091,7 @@
         <v>15</v>
       </c>
       <c r="E74">
-        <v>87.90000000000001</v>
+        <v>87.9</v>
       </c>
       <c r="F74">
         <v>1318.5</v>
@@ -4080,7 +4109,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>51</v>
       </c>
@@ -4112,7 +4141,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>52</v>
       </c>
@@ -4144,7 +4173,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>53</v>
       </c>
@@ -4176,7 +4205,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>54</v>
       </c>
@@ -4208,7 +4237,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>55</v>
       </c>
@@ -4240,7 +4269,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>56</v>
       </c>
@@ -4257,7 +4286,7 @@
         <v>269.7</v>
       </c>
       <c r="F80">
-        <v>4584.9</v>
+        <v>4584.8999999999996</v>
       </c>
       <c r="G80" t="s">
         <v>423</v>
@@ -4272,7 +4301,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>57</v>
       </c>
@@ -4304,7 +4333,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>58</v>
       </c>
@@ -4336,7 +4365,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>59</v>
       </c>
@@ -4368,7 +4397,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>60</v>
       </c>
@@ -4382,7 +4411,7 @@
         <v>25</v>
       </c>
       <c r="E84">
-        <v>67.54000000000001</v>
+        <v>67.540000000000006</v>
       </c>
       <c r="F84">
         <v>1688.5</v>
@@ -4400,7 +4429,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>61</v>
       </c>
@@ -4432,7 +4461,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>62</v>
       </c>
@@ -4464,7 +4493,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>63</v>
       </c>
@@ -4496,7 +4525,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="88" spans="1:10">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>64</v>
       </c>
@@ -4528,7 +4557,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>65</v>
       </c>
@@ -4560,7 +4589,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>66</v>
       </c>
@@ -4592,7 +4621,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>67</v>
       </c>
@@ -4606,7 +4635,7 @@
         <v>16</v>
       </c>
       <c r="E91">
-        <v>87.90000000000001</v>
+        <v>87.9</v>
       </c>
       <c r="F91">
         <v>1406.4</v>
@@ -4624,7 +4653,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>19</v>
       </c>
@@ -4653,7 +4682,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>20</v>
       </c>
@@ -4664,7 +4693,7 @@
         <v>20</v>
       </c>
       <c r="E93">
-        <v>588.45</v>
+        <v>588.45000000000005</v>
       </c>
       <c r="F93">
         <v>11769</v>
@@ -4682,7 +4711,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>21</v>
       </c>
@@ -4711,7 +4740,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>22</v>
       </c>
@@ -4740,7 +4769,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>23</v>
       </c>
@@ -4769,7 +4798,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>24</v>
       </c>
@@ -4798,7 +4827,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>68</v>
       </c>
@@ -4827,7 +4856,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>69</v>
       </c>
@@ -4856,7 +4885,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>70</v>
       </c>
@@ -4885,7 +4914,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>56</v>
       </c>
@@ -4899,10 +4928,10 @@
         <v>60</v>
       </c>
       <c r="E101">
-        <v>80.54000000000001</v>
+        <v>80.540000000000006</v>
       </c>
       <c r="F101">
-        <v>4832.4</v>
+        <v>4832.3999999999996</v>
       </c>
       <c r="G101" t="s">
         <v>423</v>
@@ -4917,7 +4946,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>70</v>
       </c>
@@ -4949,7 +4978,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="103" spans="1:10">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>71</v>
       </c>
@@ -4981,7 +5010,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>72</v>
       </c>
@@ -5013,7 +5042,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>73</v>
       </c>
@@ -5027,7 +5056,7 @@
         <v>10</v>
       </c>
       <c r="E105">
-        <v>316.4</v>
+        <v>316.39999999999998</v>
       </c>
       <c r="F105">
         <v>3164</v>
@@ -5045,7 +5074,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>74</v>
       </c>
@@ -5062,7 +5091,7 @@
         <v>2429.44</v>
       </c>
       <c r="F106">
-        <v>36441.6</v>
+        <v>36441.599999999999</v>
       </c>
       <c r="G106" t="s">
         <v>423</v>
@@ -5077,7 +5106,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>75</v>
       </c>
@@ -5109,7 +5138,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>76</v>
       </c>
@@ -5123,7 +5152,7 @@
         <v>80</v>
       </c>
       <c r="E108">
-        <v>33.3</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="F108">
         <v>2664</v>
@@ -5141,7 +5170,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>77</v>
       </c>
@@ -5158,7 +5187,7 @@
         <v>38.72</v>
       </c>
       <c r="F109">
-        <v>1161.6</v>
+        <v>1161.5999999999999</v>
       </c>
       <c r="G109" t="s">
         <v>424</v>
@@ -5173,7 +5202,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>78</v>
       </c>
@@ -5190,7 +5219,7 @@
         <v>84.56</v>
       </c>
       <c r="F110">
-        <v>1268.4</v>
+        <v>1268.4000000000001</v>
       </c>
       <c r="G110" t="s">
         <v>424</v>
@@ -5205,7 +5234,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>79</v>
       </c>
@@ -5222,7 +5251,7 @@
         <v>83.16</v>
       </c>
       <c r="F111">
-        <v>4989.6</v>
+        <v>4989.6000000000004</v>
       </c>
       <c r="G111" t="s">
         <v>423</v>
@@ -5237,7 +5266,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>80</v>
       </c>
@@ -5269,7 +5298,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>81</v>
       </c>
@@ -5301,7 +5330,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="114" spans="1:10">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>82</v>
       </c>
@@ -5333,7 +5362,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>83</v>
       </c>
@@ -5365,7 +5394,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="116" spans="1:10">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>84</v>
       </c>
@@ -5382,7 +5411,7 @@
         <v>447.11</v>
       </c>
       <c r="F116">
-        <v>8942.200000000001</v>
+        <v>8942.2000000000007</v>
       </c>
       <c r="G116" t="s">
         <v>423</v>
@@ -5397,7 +5426,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>85</v>
       </c>
@@ -5429,7 +5458,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>86</v>
       </c>
@@ -5443,7 +5472,7 @@
         <v>30</v>
       </c>
       <c r="E118">
-        <v>39.34</v>
+        <v>39.340000000000003</v>
       </c>
       <c r="F118">
         <v>1180.2</v>
@@ -5461,7 +5490,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="119" spans="1:10">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>87</v>
       </c>
@@ -5493,7 +5522,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="120" spans="1:10">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>88</v>
       </c>
@@ -5507,7 +5536,7 @@
         <v>20</v>
       </c>
       <c r="E120">
-        <v>39.34</v>
+        <v>39.340000000000003</v>
       </c>
       <c r="F120">
         <v>786.8</v>
@@ -5525,7 +5554,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>89</v>
       </c>
@@ -5542,7 +5571,7 @@
         <v>41.87</v>
       </c>
       <c r="F121">
-        <v>1256.1</v>
+        <v>1256.0999999999999</v>
       </c>
       <c r="G121" t="s">
         <v>423</v>
@@ -5557,7 +5586,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="122" spans="1:10">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>90</v>
       </c>
@@ -5589,7 +5618,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="123" spans="1:10">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>91</v>
       </c>
@@ -5603,7 +5632,7 @@
         <v>10</v>
       </c>
       <c r="E123">
-        <v>2124.78</v>
+        <v>2124.7800000000002</v>
       </c>
       <c r="F123">
         <v>21247.8</v>
@@ -5621,7 +5650,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="124" spans="1:10">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>92</v>
       </c>
@@ -5653,7 +5682,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="125" spans="1:10">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>93</v>
       </c>
@@ -5685,7 +5714,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="126" spans="1:10">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>94</v>
       </c>
@@ -5717,7 +5746,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>95</v>
       </c>
@@ -5749,7 +5778,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>96</v>
       </c>
@@ -5781,7 +5810,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="129" spans="1:10">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>97</v>
       </c>
@@ -5813,7 +5842,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>98</v>
       </c>
@@ -5845,7 +5874,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="131" spans="1:10">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>99</v>
       </c>
@@ -5877,7 +5906,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="132" spans="1:10">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>100</v>
       </c>
@@ -5909,7 +5938,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="133" spans="1:10">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>101</v>
       </c>
@@ -5941,7 +5970,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="134" spans="1:10">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>102</v>
       </c>
@@ -5973,7 +6002,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>103</v>
       </c>
@@ -5987,7 +6016,7 @@
         <v>24</v>
       </c>
       <c r="E135">
-        <v>1205.16</v>
+        <v>1205.1600000000001</v>
       </c>
       <c r="F135">
         <v>28923.84</v>
@@ -6005,7 +6034,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="136" spans="1:10">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>104</v>
       </c>
@@ -6037,7 +6066,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="137" spans="1:10">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>105</v>
       </c>
@@ -6069,7 +6098,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="138" spans="1:10">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>106</v>
       </c>
@@ -6086,7 +6115,7 @@
         <v>365.02</v>
       </c>
       <c r="F138">
-        <v>29201.6</v>
+        <v>29201.599999999999</v>
       </c>
       <c r="G138" t="s">
         <v>423</v>
@@ -6101,7 +6130,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="139" spans="1:10">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>107</v>
       </c>
@@ -6115,7 +6144,7 @@
         <v>30</v>
       </c>
       <c r="E139">
-        <v>855.1900000000001</v>
+        <v>855.19</v>
       </c>
       <c r="F139">
         <v>25655.7</v>
@@ -6133,7 +6162,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="140" spans="1:10">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>108</v>
       </c>
@@ -6147,7 +6176,7 @@
         <v>20</v>
       </c>
       <c r="E140">
-        <v>577.67</v>
+        <v>577.66999999999996</v>
       </c>
       <c r="F140">
         <v>11553.4</v>
@@ -6165,7 +6194,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="141" spans="1:10">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>109</v>
       </c>
@@ -6197,7 +6226,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="142" spans="1:10">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>110</v>
       </c>
@@ -6211,7 +6240,7 @@
         <v>10</v>
       </c>
       <c r="E142">
-        <v>2417.43</v>
+        <v>2417.4299999999998</v>
       </c>
       <c r="F142">
         <v>24174.3</v>
@@ -6229,7 +6258,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="143" spans="1:10">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>111</v>
       </c>
@@ -6243,7 +6272,7 @@
         <v>3428.68</v>
       </c>
       <c r="F143">
-        <v>34286.8</v>
+        <v>34286.800000000003</v>
       </c>
       <c r="G143" t="s">
         <v>423</v>
@@ -6258,7 +6287,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="144" spans="1:10">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>10</v>
       </c>
@@ -6290,7 +6319,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="145" spans="1:10">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>11</v>
       </c>
@@ -6322,7 +6351,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="146" spans="1:10">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>12</v>
       </c>
@@ -6354,7 +6383,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="147" spans="1:10">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>13</v>
       </c>
@@ -6386,7 +6415,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="148" spans="1:10">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>14</v>
       </c>
@@ -6418,7 +6447,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="149" spans="1:10">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>15</v>
       </c>
@@ -6450,7 +6479,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="150" spans="1:10">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>16</v>
       </c>
@@ -6482,7 +6511,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="151" spans="1:10">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>17</v>
       </c>
@@ -6514,7 +6543,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="152" spans="1:10">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -6531,7 +6560,7 @@
         <v>187.9</v>
       </c>
       <c r="F152">
-        <v>563.7</v>
+        <v>563.70000000000005</v>
       </c>
       <c r="G152" t="s">
         <v>423</v>
@@ -6546,7 +6575,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="153" spans="1:10">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>22</v>
       </c>
@@ -6578,7 +6607,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="154" spans="1:10">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>23</v>
       </c>
@@ -6610,7 +6639,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="155" spans="1:10">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>24</v>
       </c>
@@ -6642,7 +6671,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="156" spans="1:10">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>25</v>
       </c>
@@ -6674,7 +6703,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="157" spans="1:10">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>26</v>
       </c>
@@ -6706,7 +6735,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="158" spans="1:10">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>27</v>
       </c>
@@ -6738,7 +6767,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="159" spans="1:10">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>28</v>
       </c>
@@ -6770,7 +6799,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="160" spans="1:10">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>29</v>
       </c>
@@ -6802,7 +6831,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="161" spans="1:10">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>30</v>
       </c>
@@ -6834,7 +6863,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="162" spans="1:10">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>31</v>
       </c>
@@ -6866,7 +6895,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="163" spans="1:10">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>32</v>
       </c>
@@ -6898,7 +6927,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="164" spans="1:10">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>34</v>
       </c>
@@ -6915,7 +6944,7 @@
         <v>12829.4</v>
       </c>
       <c r="F164">
-        <v>38488.2</v>
+        <v>38488.199999999997</v>
       </c>
       <c r="G164" t="s">
         <v>423</v>
@@ -6930,7 +6959,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="165" spans="1:10">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>36</v>
       </c>
@@ -6962,7 +6991,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="166" spans="1:10">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>37</v>
       </c>
@@ -6994,7 +7023,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="167" spans="1:10">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>39</v>
       </c>
@@ -7026,7 +7055,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="168" spans="1:10">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>43</v>
       </c>
@@ -7058,7 +7087,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="169" spans="1:10">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>45</v>
       </c>
@@ -7090,7 +7119,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="170" spans="1:10">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>46</v>
       </c>
@@ -7122,7 +7151,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="171" spans="1:10">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>48</v>
       </c>
@@ -7154,7 +7183,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="172" spans="1:10">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>49</v>
       </c>
@@ -7186,7 +7215,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="173" spans="1:10">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>12</v>
       </c>
@@ -7215,7 +7244,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="174" spans="1:10">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>16</v>
       </c>
@@ -7244,7 +7273,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="175" spans="1:10">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>33</v>
       </c>
@@ -7273,7 +7302,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="176" spans="1:10">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>37</v>
       </c>
@@ -7302,7 +7331,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="177" spans="1:10">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>39</v>
       </c>
@@ -7331,7 +7360,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="178" spans="1:10">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>41</v>
       </c>
@@ -7360,7 +7389,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="179" spans="1:10">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>42</v>
       </c>
@@ -7389,7 +7418,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="180" spans="1:10">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>10</v>
       </c>
@@ -7421,7 +7450,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="181" spans="1:10">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>11</v>
       </c>
@@ -7453,7 +7482,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="182" spans="1:10">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>12</v>
       </c>
@@ -7485,7 +7514,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="183" spans="1:10">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>13</v>
       </c>
@@ -7517,7 +7546,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="184" spans="1:10">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>14</v>
       </c>
@@ -7549,7 +7578,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="185" spans="1:10">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>15</v>
       </c>
@@ -7581,7 +7610,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="186" spans="1:10">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>16</v>
       </c>
@@ -7613,7 +7642,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="187" spans="1:10">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>17</v>
       </c>
@@ -7645,7 +7674,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="188" spans="1:10">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>18</v>
       </c>
@@ -7677,7 +7706,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="189" spans="1:10">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>19</v>
       </c>
@@ -7709,7 +7738,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="190" spans="1:10">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>20</v>
       </c>
@@ -7741,7 +7770,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="191" spans="1:10">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>21</v>
       </c>
@@ -7773,7 +7802,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="192" spans="1:10">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>22</v>
       </c>
@@ -7805,7 +7834,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="193" spans="1:10">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>23</v>
       </c>
@@ -7837,7 +7866,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="194" spans="1:10">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>24</v>
       </c>
@@ -7869,7 +7898,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="195" spans="1:10">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>25</v>
       </c>
@@ -7901,7 +7930,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="196" spans="1:10">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>26</v>
       </c>
@@ -7933,7 +7962,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="197" spans="1:10">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>27</v>
       </c>
@@ -7965,7 +7994,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="198" spans="1:10">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>28</v>
       </c>
@@ -7997,7 +8026,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="199" spans="1:10">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>29</v>
       </c>
